--- a/data/trans_orig/Q45A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q45A_R-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de haber estado expuesto al sol entre las 12 de la mañana y las 5 de la tarde el pasado verano en 2007</t>
+          <t>Población según la frecuencia de haber estado expuesto al sol entre las 12 de la mañana y las 5 de la tarde el pasado verano en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22818</t>
+          <t>22971</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44400</t>
+          <t>46086</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14449</t>
+          <t>14737</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>33642</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42785</t>
+          <t>41866</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72752</t>
+          <t>71319</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75743</t>
+          <t>75325</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>113682</t>
+          <t>113626</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42173</t>
+          <t>41418</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70540</t>
+          <t>71096</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>125188</t>
+          <t>127586</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174289</t>
+          <t>174538</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>360895</t>
+          <t>356766</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>419173</t>
+          <t>420113</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>491383</t>
+          <t>488461</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>559577</t>
+          <t>558194</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>871038</t>
+          <t>871555</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>960309</t>
+          <t>962912</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,05%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>209820</t>
+          <t>210719</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>261563</t>
+          <t>261768</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>277213</t>
+          <t>277523</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>336766</t>
+          <t>337849</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>499363</t>
+          <t>501244</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>581773</t>
+          <t>582349</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>255200</t>
+          <t>253779</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>310263</t>
+          <t>310797</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>371940</t>
+          <t>373530</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>436818</t>
+          <t>437647</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>641859</t>
+          <t>641704</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>725602</t>
+          <t>731428</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20003</t>
+          <t>20119</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44317</t>
+          <t>43046</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16099</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35235</t>
+          <t>35515</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40838</t>
+          <t>40476</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70847</t>
+          <t>70440</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>166493</t>
+          <t>166303</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>218837</t>
+          <t>220721</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138463</t>
+          <t>135977</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>183625</t>
+          <t>185319</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>314979</t>
+          <t>313583</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>384858</t>
+          <t>384693</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>866263</t>
+          <t>861335</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>945551</t>
+          <t>944882</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>809130</t>
+          <t>807003</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>888786</t>
+          <t>887824</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1693380</t>
+          <t>1691629</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1809233</t>
+          <t>1809005</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,13%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>309070</t>
+          <t>305836</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>376098</t>
+          <t>372637</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>302291</t>
+          <t>299993</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>364560</t>
+          <t>365880</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>628638</t>
+          <t>623918</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>720667</t>
+          <t>722151</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>199467</t>
+          <t>199208</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>259596</t>
+          <t>259346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>193324</t>
+          <t>196433</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>250728</t>
+          <t>251766</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413374</t>
+          <t>409126</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>493103</t>
+          <t>493805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13056</t>
+          <t>12933</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>17053</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>8168</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23703</t>
+          <t>25190</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45871</t>
+          <t>46042</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75817</t>
+          <t>75422</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40408</t>
+          <t>41882</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>67731</t>
+          <t>69429</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>93756</t>
+          <t>93715</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>133379</t>
+          <t>132818</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>245645</t>
+          <t>247937</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>293136</t>
+          <t>294562</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>237118</t>
+          <t>237205</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>278250</t>
+          <t>282540</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>498545</t>
+          <t>499693</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>562976</t>
+          <t>564512</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,92%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>110301</t>
+          <t>110273</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>151374</t>
+          <t>150189</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69128</t>
+          <t>67802</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>102232</t>
+          <t>101956</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>188156</t>
+          <t>185702</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>243072</t>
+          <t>240365</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67874</t>
+          <t>68731</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>103824</t>
+          <t>105127</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53463</t>
+          <t>55150</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>85595</t>
+          <t>87971</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>130092</t>
+          <t>132202</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>179999</t>
+          <t>179068</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52608</t>
+          <t>52802</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86265</t>
+          <t>86352</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42338</t>
+          <t>42664</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72705</t>
+          <t>72172</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>102408</t>
+          <t>101674</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>151091</t>
+          <t>148354</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>303261</t>
+          <t>309197</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>378377</t>
+          <t>378323</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>239081</t>
+          <t>238811</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>300719</t>
+          <t>301688</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>565077</t>
+          <t>567074</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>655922</t>
+          <t>660112</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1503409</t>
+          <t>1504025</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1616120</t>
+          <t>1622779</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,82 +3019,82 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>49,54%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1633301</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>1579634</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>1698815</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>48,33%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>46,75%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>50,27%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>3140</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>3196122</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>3118734</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>3283400</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>48,03%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>46,86%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
           <t>49,34%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1605</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>1633301</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>1572951</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1689033</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>48,33%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>46,55%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>49,98%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3140</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3196122</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3116389</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3282669</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>48,03%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>46,83%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>49,33%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>660485</t>
+          <t>658849</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>755112</t>
+          <t>750555</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>674252</t>
+          <t>674272</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>771439</t>
+          <t>768681</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1364248</t>
+          <t>1356746</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1497118</t>
+          <t>1496805</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>551838</t>
+          <t>554201</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>640926</t>
+          <t>642961</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>651926</t>
+          <t>653794</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>746930</t>
+          <t>747492</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1229819</t>
+          <t>1230207</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1364749</t>
+          <t>1362563</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de haber estado expuesto al sol entre las 12 de la mañana y las 5 de la tarde el pasado verano en 2012</t>
+          <t>Población según la frecuencia de haber estado expuesto al sol entre las 12 de la mañana y las 5 de la tarde el pasado verano en 2012 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19838</t>
+          <t>20429</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19494</t>
+          <t>21235</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>15216</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34848</t>
+          <t>34088</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47818</t>
+          <t>47562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80098</t>
+          <t>79232</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44411</t>
+          <t>43362</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73223</t>
+          <t>74027</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96970</t>
+          <t>98187</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>140555</t>
+          <t>141772</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>220842</t>
+          <t>220467</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>276519</t>
+          <t>276383</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>277556</t>
+          <t>272987</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>339093</t>
+          <t>337575</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>513449</t>
+          <t>514931</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>596774</t>
+          <t>595086</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>198701</t>
+          <t>196338</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>253608</t>
+          <t>249044</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>319205</t>
+          <t>319283</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>383366</t>
+          <t>386545</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>533618</t>
+          <t>533091</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>620002</t>
+          <t>618377</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>396041</t>
+          <t>399002</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>460468</t>
+          <t>459032</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>575949</t>
+          <t>573764</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>649330</t>
+          <t>650693</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>993130</t>
+          <t>991569</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1090240</t>
+          <t>1088160</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,1%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32517</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62382</t>
+          <t>61034</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21018</t>
+          <t>20392</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42344</t>
+          <t>43499</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59099</t>
+          <t>59308</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96718</t>
+          <t>95250</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>219047</t>
+          <t>217834</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>280826</t>
+          <t>275696</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>176144</t>
+          <t>175255</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>232484</t>
+          <t>229548</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>411020</t>
+          <t>406135</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>491430</t>
+          <t>491447</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>769140</t>
+          <t>774258</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>863054</t>
+          <t>860296</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>671620</t>
+          <t>671450</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>755414</t>
+          <t>758088</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1464263</t>
+          <t>1464182</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1592714</t>
+          <t>1590338</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,8%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>358727</t>
+          <t>359044</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>433415</t>
+          <t>430162</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>315446</t>
+          <t>311006</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>381449</t>
+          <t>379570</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>688962</t>
+          <t>689937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>789637</t>
+          <t>789589</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>419821</t>
+          <t>422133</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>500085</t>
+          <t>499917</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>425391</t>
+          <t>423332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>498112</t>
+          <t>499059</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>862686</t>
+          <t>861980</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>970649</t>
+          <t>969201</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>16596</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19874</t>
+          <t>20389</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34683</t>
+          <t>34720</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62263</t>
+          <t>61262</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36042</t>
+          <t>36652</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64605</t>
+          <t>64761</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>77272</t>
+          <t>77519</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>114929</t>
+          <t>117816</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>203678</t>
+          <t>203033</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>246747</t>
+          <t>248581</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>170365</t>
+          <t>169868</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>214846</t>
+          <t>217084</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386478</t>
+          <t>384709</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>450457</t>
+          <t>453816</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83550</t>
+          <t>84965</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>121246</t>
+          <t>124196</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88094</t>
+          <t>88082</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>125214</t>
+          <t>126211</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>179268</t>
+          <t>182482</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>233845</t>
+          <t>234374</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85100</t>
+          <t>84979</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123715</t>
+          <t>124576</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>80394</t>
+          <t>82882</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>120325</t>
+          <t>118227</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>179598</t>
+          <t>179063</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>232669</t>
+          <t>234321</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43992</t>
+          <t>44480</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>78977</t>
+          <t>77907</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38282</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67576</t>
+          <t>67126</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90482</t>
+          <t>90862</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>133623</t>
+          <t>135809</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>318842</t>
+          <t>320166</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>395229</t>
+          <t>393052</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>278974</t>
+          <t>276718</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>349854</t>
+          <t>341820</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>617109</t>
+          <t>616033</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>715659</t>
+          <t>712976</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1230832</t>
+          <t>1229414</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1353427</t>
+          <t>1349732</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1157536</t>
+          <t>1157089</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1276481</t>
+          <t>1278563</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2423405</t>
+          <t>2414587</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2584545</t>
+          <t>2582632</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>672169</t>
+          <t>673074</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>777249</t>
+          <t>774241</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>746963</t>
+          <t>753741</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>851489</t>
+          <t>853896</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1451583</t>
+          <t>1448841</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1591814</t>
+          <t>1602318</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>931732</t>
+          <t>933054</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1040418</t>
+          <t>1047456</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1115685</t>
+          <t>1117397</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1228958</t>
+          <t>1234069</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2085580</t>
+          <t>2086465</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2239433</t>
+          <t>2245623</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de haber estado expuesto al sol entre las 12 de la mañana y las 5 de la tarde el pasado verano en 2016</t>
+          <t>Población según la frecuencia de haber estado expuesto al sol entre las 12 de la mañana y las 5 de la tarde el pasado verano en 2016 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17615</t>
+          <t>17978</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24038</t>
+          <t>23607</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51764</t>
+          <t>52062</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82673</t>
+          <t>82262</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40599</t>
+          <t>40867</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71960</t>
+          <t>70894</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99004</t>
+          <t>99617</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>140957</t>
+          <t>142304</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>179984</t>
+          <t>179788</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>231011</t>
+          <t>227715</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>182710</t>
+          <t>184557</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>236043</t>
+          <t>240134</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>375119</t>
+          <t>374902</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>448436</t>
+          <t>447572</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>228279</t>
+          <t>231356</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>281384</t>
+          <t>281301</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>295640</t>
+          <t>296570</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>360360</t>
+          <t>359048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>539313</t>
+          <t>545227</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>620485</t>
+          <t>621166</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>199184</t>
+          <t>199501</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>248164</t>
+          <t>248661</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>362806</t>
+          <t>359332</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>427558</t>
+          <t>425068</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>577593</t>
+          <t>579020</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>660025</t>
+          <t>661782</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,94%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>16248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36551</t>
+          <t>36826</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17232</t>
+          <t>17425</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38927</t>
+          <t>40462</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38675</t>
+          <t>38421</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69359</t>
+          <t>68273</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>280452</t>
+          <t>278554</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>348248</t>
+          <t>347608</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>224332</t>
+          <t>222812</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>283323</t>
+          <t>286602</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>523900</t>
+          <t>526860</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>609158</t>
+          <t>614483</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>740414</t>
+          <t>743196</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>832345</t>
+          <t>831839</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>687698</t>
+          <t>685662</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>774377</t>
+          <t>772599</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1456517</t>
+          <t>1453671</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1582490</t>
+          <t>1576624</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>562254</t>
+          <t>559531</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>644448</t>
+          <t>642558</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>585047</t>
+          <t>585634</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>669518</t>
+          <t>670213</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1161557</t>
+          <t>1164317</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1284451</t>
+          <t>1277538</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>313275</t>
+          <t>313455</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>382883</t>
+          <t>382242</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>315489</t>
+          <t>314440</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386665</t>
+          <t>384777</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>650374</t>
+          <t>649680</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>752504</t>
+          <t>748896</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12516</t>
+          <t>12555</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>5017</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>17272</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,47 +8064,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>9173</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>24851</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>15038</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>8212</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>24628</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78394</t>
+          <t>79398</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115496</t>
+          <t>115031</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70042</t>
+          <t>70922</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103551</t>
+          <t>106466</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>160217</t>
+          <t>157832</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>208620</t>
+          <t>211965</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>193412</t>
+          <t>190998</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>241653</t>
+          <t>239297</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>201312</t>
+          <t>201883</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>246845</t>
+          <t>247620</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>403556</t>
+          <t>406835</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>470811</t>
+          <t>471934</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>153474</t>
+          <t>151997</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>199151</t>
+          <t>198790</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>130888</t>
+          <t>128020</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>171365</t>
+          <t>169782</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>292470</t>
+          <t>292257</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>356062</t>
+          <t>356633</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40413</t>
+          <t>38897</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>71636</t>
+          <t>68615</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65880</t>
+          <t>63879</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>99351</t>
+          <t>98488</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>113290</t>
+          <t>111587</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>159079</t>
+          <t>156903</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23453</t>
+          <t>23809</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48954</t>
+          <t>48587</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33916</t>
+          <t>32947</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61218</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65968</t>
+          <t>63487</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>103022</t>
+          <t>99297</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>439391</t>
+          <t>433189</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>520721</t>
+          <t>518311</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>355643</t>
+          <t>358284</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>430922</t>
+          <t>426698</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>818318</t>
+          <t>815121</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>924938</t>
+          <t>924587</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1148159</t>
+          <t>1149979</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1256783</t>
+          <t>1264724</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1105685</t>
+          <t>1102149</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1222541</t>
+          <t>1221103</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2289005</t>
+          <t>2293045</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2452875</t>
+          <t>2443878</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>975330</t>
+          <t>976628</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1082931</t>
+          <t>1087619</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1048254</t>
+          <t>1041136</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1160175</t>
+          <t>1156482</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2049740</t>
+          <t>2050456</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2199976</t>
+          <t>2210660</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>580069</t>
+          <t>577137</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>672314</t>
+          <t>666976</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>769600</t>
+          <t>772902</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>878460</t>
+          <t>877680</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1382220</t>
+          <t>1384310</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1521885</t>
+          <t>1517781</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q45A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q45A_R-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22971</t>
+          <t>22896</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46086</t>
+          <t>45125</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14737</t>
+          <t>14284</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33642</t>
+          <t>34981</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41866</t>
+          <t>41781</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71319</t>
+          <t>73570</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75325</t>
+          <t>76211</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>113626</t>
+          <t>113288</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41418</t>
+          <t>41053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71096</t>
+          <t>69491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127586</t>
+          <t>125525</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174538</t>
+          <t>172902</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>356766</t>
+          <t>360017</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>420113</t>
+          <t>420565</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>488461</t>
+          <t>490174</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>558194</t>
+          <t>560017</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>871555</t>
+          <t>867434</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>962912</t>
+          <t>964766</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,12%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>210719</t>
+          <t>209633</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>261768</t>
+          <t>259848</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>277523</t>
+          <t>280957</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>337849</t>
+          <t>338653</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>501244</t>
+          <t>504307</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>582349</t>
+          <t>581484</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>253779</t>
+          <t>253409</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>310797</t>
+          <t>309001</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>373530</t>
+          <t>374032</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>437647</t>
+          <t>441731</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>641704</t>
+          <t>642069</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731428</t>
+          <t>729353</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20119</t>
+          <t>20260</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43046</t>
+          <t>43748</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15517</t>
+          <t>16322</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35515</t>
+          <t>36947</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40476</t>
+          <t>41555</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70440</t>
+          <t>72204</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>166303</t>
+          <t>166231</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>220721</t>
+          <t>217731</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>135977</t>
+          <t>138057</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>185319</t>
+          <t>182621</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>313583</t>
+          <t>315250</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>384693</t>
+          <t>387694</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>861335</t>
+          <t>856137</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>944882</t>
+          <t>940193</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>807003</t>
+          <t>807917</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>887824</t>
+          <t>888187</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1691629</t>
+          <t>1696017</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1809005</t>
+          <t>1810040</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,17%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>305836</t>
+          <t>310807</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>372637</t>
+          <t>376232</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>299993</t>
+          <t>300529</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>365880</t>
+          <t>363748</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>623918</t>
+          <t>628566</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>722151</t>
+          <t>721510</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>199208</t>
+          <t>203058</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>259346</t>
+          <t>261408</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>196433</t>
+          <t>198153</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>251766</t>
+          <t>255362</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>409126</t>
+          <t>414730</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>493805</t>
+          <t>494604</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2470</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12933</t>
+          <t>13257</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17053</t>
+          <t>16590</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25190</t>
+          <t>25836</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46042</t>
+          <t>45918</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75422</t>
+          <t>77251</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41882</t>
+          <t>42161</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69429</t>
+          <t>69398</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>93715</t>
+          <t>93394</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>132818</t>
+          <t>136297</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>247937</t>
+          <t>246742</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>294562</t>
+          <t>295293</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>237205</t>
+          <t>237125</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>282540</t>
+          <t>280236</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>499693</t>
+          <t>494319</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>564512</t>
+          <t>565070</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,98%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>110273</t>
+          <t>111432</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>150189</t>
+          <t>150674</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67802</t>
+          <t>69717</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>101956</t>
+          <t>102910</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>185702</t>
+          <t>188011</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>240365</t>
+          <t>240175</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68731</t>
+          <t>68634</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>105127</t>
+          <t>107225</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55150</t>
+          <t>54507</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>87971</t>
+          <t>86330</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>132202</t>
+          <t>133807</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>179068</t>
+          <t>181028</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52802</t>
+          <t>54027</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86352</t>
+          <t>86561</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42664</t>
+          <t>42961</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72172</t>
+          <t>72004</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>101674</t>
+          <t>102298</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>148354</t>
+          <t>149196</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>309197</t>
+          <t>306719</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>378323</t>
+          <t>377718</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>238811</t>
+          <t>238038</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>301688</t>
+          <t>301140</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>567074</t>
+          <t>568317</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>660112</t>
+          <t>664473</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1504025</t>
+          <t>1505457</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1622779</t>
+          <t>1622129</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1579634</t>
+          <t>1577997</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1698815</t>
+          <t>1692817</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3118734</t>
+          <t>3123025</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3283400</t>
+          <t>3280236</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,29%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>658849</t>
+          <t>659477</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>750555</t>
+          <t>753724</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>674272</t>
+          <t>678647</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>768681</t>
+          <t>772300</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1356746</t>
+          <t>1368145</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1496805</t>
+          <t>1500571</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>554201</t>
+          <t>551661</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>642961</t>
+          <t>641267</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>653794</t>
+          <t>653195</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>747492</t>
+          <t>746162</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1230207</t>
+          <t>1232305</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1362563</t>
+          <t>1359440</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20429</t>
+          <t>19418</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21235</t>
+          <t>20026</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15216</t>
+          <t>14809</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34088</t>
+          <t>34298</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47562</t>
+          <t>47665</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79232</t>
+          <t>78449</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43362</t>
+          <t>43327</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74027</t>
+          <t>73439</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98187</t>
+          <t>99852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141772</t>
+          <t>142772</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>220467</t>
+          <t>218458</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>276383</t>
+          <t>273934</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>272987</t>
+          <t>272049</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>337575</t>
+          <t>336233</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>514931</t>
+          <t>512017</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>595086</t>
+          <t>596072</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>196338</t>
+          <t>197666</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>249044</t>
+          <t>254217</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>319283</t>
+          <t>319730</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>386545</t>
+          <t>382611</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>533091</t>
+          <t>530435</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>618377</t>
+          <t>620045</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399002</t>
+          <t>396366</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>459032</t>
+          <t>460154</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>573764</t>
+          <t>577060</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>650693</t>
+          <t>649943</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>991569</t>
+          <t>994277</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1088160</t>
+          <t>1090923</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,22%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32294</t>
+          <t>32597</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61034</t>
+          <t>61639</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20392</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43499</t>
+          <t>42751</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59308</t>
+          <t>58869</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95250</t>
+          <t>95504</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>217834</t>
+          <t>216795</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>275696</t>
+          <t>278761</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>175255</t>
+          <t>175220</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>229548</t>
+          <t>232233</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>406135</t>
+          <t>413067</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>491447</t>
+          <t>491441</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>774258</t>
+          <t>772127</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>860296</t>
+          <t>864992</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>671450</t>
+          <t>670213</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>758088</t>
+          <t>752858</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1464182</t>
+          <t>1475742</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1590338</t>
+          <t>1591649</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,84%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>359044</t>
+          <t>357819</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>430162</t>
+          <t>431450</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>311006</t>
+          <t>312038</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>379570</t>
+          <t>378354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>689937</t>
+          <t>690079</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>789589</t>
+          <t>790488</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>422133</t>
+          <t>418882</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>499917</t>
+          <t>497743</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>423332</t>
+          <t>427094</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>499059</t>
+          <t>503881</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>861980</t>
+          <t>868224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>969201</t>
+          <t>976102</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16596</t>
+          <t>16951</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>6543</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20389</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34720</t>
+          <t>34516</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61262</t>
+          <t>61764</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36652</t>
+          <t>36711</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64761</t>
+          <t>65267</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>77519</t>
+          <t>76589</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117816</t>
+          <t>116806</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>203033</t>
+          <t>200203</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>248581</t>
+          <t>247900</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>169868</t>
+          <t>172773</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>217084</t>
+          <t>217998</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>384709</t>
+          <t>386879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>453816</t>
+          <t>449921</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>47,92%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84965</t>
+          <t>84743</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124196</t>
+          <t>125029</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88082</t>
+          <t>86490</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>126211</t>
+          <t>123554</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>182482</t>
+          <t>180576</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>234374</t>
+          <t>235512</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>84979</t>
+          <t>84726</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>124576</t>
+          <t>125185</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,49 +5522,49 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>26,02%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>99980</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>80534</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>118486</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>21,85%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>17,6%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>25,89%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>99980</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>82882</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>118227</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>21,85%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>18,11%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>25,83%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>174</t>
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>179063</t>
+          <t>177108</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>234321</t>
+          <t>232156</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44480</t>
+          <t>44926</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77907</t>
+          <t>77755</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38130</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67126</t>
+          <t>65931</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90862</t>
+          <t>89048</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>135809</t>
+          <t>132903</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>320166</t>
+          <t>321088</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>393052</t>
+          <t>394472</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>276718</t>
+          <t>276923</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>341820</t>
+          <t>345600</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>616033</t>
+          <t>616597</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>712976</t>
+          <t>717054</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1229414</t>
+          <t>1233305</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1349732</t>
+          <t>1350651</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1157089</t>
+          <t>1155789</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1278563</t>
+          <t>1271357</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2414587</t>
+          <t>2421389</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2582632</t>
+          <t>2587833</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>673074</t>
+          <t>671759</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>774241</t>
+          <t>769606</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>753741</t>
+          <t>748452</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>853896</t>
+          <t>852126</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1448841</t>
+          <t>1450310</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1602318</t>
+          <t>1594192</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>933054</t>
+          <t>934687</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1047456</t>
+          <t>1042826</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1117397</t>
+          <t>1119419</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1234069</t>
+          <t>1235185</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2086465</t>
+          <t>2078952</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2245623</t>
+          <t>2234860</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>10026</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17978</t>
+          <t>17975</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23607</t>
+          <t>23247</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52062</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82262</t>
+          <t>81557</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40867</t>
+          <t>40287</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70894</t>
+          <t>68861</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99617</t>
+          <t>101090</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>142304</t>
+          <t>143358</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>179788</t>
+          <t>179468</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>227715</t>
+          <t>225685</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>184557</t>
+          <t>184574</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>240134</t>
+          <t>237376</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>374902</t>
+          <t>374763</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>447572</t>
+          <t>449359</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>231356</t>
+          <t>231020</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>281301</t>
+          <t>283680</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>296570</t>
+          <t>295634</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>359048</t>
+          <t>359728</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>545227</t>
+          <t>544144</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>621166</t>
+          <t>623639</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>199501</t>
+          <t>198476</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>248661</t>
+          <t>246776</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359332</t>
+          <t>361597</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>425068</t>
+          <t>427211</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>579020</t>
+          <t>578892</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>661782</t>
+          <t>662064</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16248</t>
+          <t>15580</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36826</t>
+          <t>37955</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17425</t>
+          <t>16603</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40462</t>
+          <t>38276</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38421</t>
+          <t>37972</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68273</t>
+          <t>69130</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>278554</t>
+          <t>282358</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>347608</t>
+          <t>350075</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>222812</t>
+          <t>224703</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>286602</t>
+          <t>284985</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>526860</t>
+          <t>518995</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>614483</t>
+          <t>608148</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>743196</t>
+          <t>741568</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>831839</t>
+          <t>834928</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>685662</t>
+          <t>686816</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>772599</t>
+          <t>776274</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1453671</t>
+          <t>1450616</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1576624</t>
+          <t>1576172</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,84%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>559531</t>
+          <t>557725</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>642558</t>
+          <t>642304</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>585634</t>
+          <t>586381</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>670213</t>
+          <t>671386</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1164317</t>
+          <t>1171121</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1277538</t>
+          <t>1282643</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>313455</t>
+          <t>310207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>382242</t>
+          <t>382720</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,82 +7799,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>18,47%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>351200</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>315103</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>385338</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>17,69%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>15,87%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>19,41%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>698240</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>650794</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>748792</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>17,21%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>16,04%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>18,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>351200</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>314440</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>384777</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>17,69%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>15,84%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>19,38%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>698240</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>649680</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>748896</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>17,21%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>16,01%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12555</t>
+          <t>12548</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17272</t>
+          <t>17561</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9173</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24851</t>
+          <t>23365</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79398</t>
+          <t>79086</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115031</t>
+          <t>116707</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70922</t>
+          <t>70072</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106466</t>
+          <t>105774</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>157832</t>
+          <t>158122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>211965</t>
+          <t>206826</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>190998</t>
+          <t>191970</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>239297</t>
+          <t>240331</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>201883</t>
+          <t>200824</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>247620</t>
+          <t>246890</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>406835</t>
+          <t>409534</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>471934</t>
+          <t>473601</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,25%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>151997</t>
+          <t>153298</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>198790</t>
+          <t>199184</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>128020</t>
+          <t>127864</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>169782</t>
+          <t>170283</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>292257</t>
+          <t>290063</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>356633</t>
+          <t>354537</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,38%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>39524</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68615</t>
+          <t>69595</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63879</t>
+          <t>65292</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>98488</t>
+          <t>98566</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111587</t>
+          <t>114579</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>156903</t>
+          <t>160731</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23809</t>
+          <t>23672</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48587</t>
+          <t>47192</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32947</t>
+          <t>33991</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>60974</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,42 +8746,42 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>80185</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>63825</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>99304</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>0,93%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>80185</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>63487</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>99297</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>433189</t>
+          <t>439546</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>518311</t>
+          <t>522087</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>358284</t>
+          <t>357604</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>426698</t>
+          <t>434763</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>815121</t>
+          <t>813733</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>924587</t>
+          <t>921645</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1149979</t>
+          <t>1150806</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1264724</t>
+          <t>1261851</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1102149</t>
+          <t>1110472</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1221103</t>
+          <t>1214776</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2293045</t>
+          <t>2285869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2443878</t>
+          <t>2442494</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>976628</t>
+          <t>974500</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1087619</t>
+          <t>1085717</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1041136</t>
+          <t>1042470</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1156482</t>
+          <t>1153387</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2050456</t>
+          <t>2063706</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2210660</t>
+          <t>2214126</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>577137</t>
+          <t>577935</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>666976</t>
+          <t>672056</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>772902</t>
+          <t>779134</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>877680</t>
+          <t>884007</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1384310</t>
+          <t>1383923</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1517781</t>
+          <t>1523060</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
